--- a/mp-cscene/src/main/resources/excel_template/third_party_topo_export_template.xlsx
+++ b/mp-cscene/src/main/resources/excel_template/third_party_topo_export_template.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>当前模板为第三方靶场上传本靶场拓扑到合肥演训平台模板。
 需要填写“拓扑节点”和“节点连线”两个sheet页。
@@ -43,10 +43,16 @@
     <t>节点名称（节点名称需要唯一）</t>
   </si>
   <si>
+    <t>所属靶场</t>
+  </si>
+  <si>
     <t>{.nodeType}</t>
   </si>
   <si>
     <t>{.nodeName}</t>
+  </si>
+  <si>
+    <t>{.range}</t>
   </si>
   <si>
     <t>连线起始节点名称（请选择）</t>
@@ -1242,33 +1248,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="1"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="64.25" customWidth="1"/>
     <col min="2" max="2" width="94.875" customWidth="1"/>
+    <col min="3" max="3" width="25.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="87" customHeight="1" spans="1:2">
+    <row r="1" ht="87" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
     </row>
-    <row r="2" ht="65" customHeight="1" spans="1:2">
+    <row r="2" ht="65" customHeight="1" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6" ht="15" spans="2:2">
@@ -1279,7 +1293,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A1048576" errorStyle="warning">
@@ -1305,30 +1319,30 @@
   <sheetData>
     <row r="1" ht="84" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
